--- a/daily_matches/job_matches_2026-06-15.xlsx
+++ b/daily_matches/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,52 +468,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist, Upstream Development</t>
+          <t>Python-AI_ML-GenAI- Senior Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, TensorFlow, PyTorch, Azure ML, MLflow, CI/CD, Databricks</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bc00b5480825d50</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f451b2d6561869</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
+          <t>Bioinformatics Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Spectrix Analytical Services, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,69 +521,69 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Data Lake, FastAPI, Docker, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c190ae15db8b6b40</t>
+          <t>https://www.indeed.com/viewjob?jk=d7716b1a79b7d737</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Storage Production Engineer - DGX Cloud</t>
+          <t>Intern Agentic AI Developer (Summer 2026)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Irving, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Cortex, S3, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc7041ff891635</t>
+          <t>https://www.indeed.com/viewjob?jk=fe812e6352b4299a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Python Engineer, Senior Associate</t>
+          <t>Senior Marketing Decision Scientist II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,349 +591,349 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Jenkins, Terraform, Git, PostgreSQL, Polars, Python</t>
+          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9571f04802a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=c24fa6b84d831ce2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>HackerTrail</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Kubernetes, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92c8346ccf59f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3a78e150cfaec939</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Nintex</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa9095bb6efbc19</t>
+          <t>https://www.indeed.com/viewjob?jk=884a331450111479</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Software Engineer II, AI Labs &amp; Foundations</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aston, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3118e2cb185b7965</t>
+          <t>https://www.indeed.com/viewjob?jk=373129946e19ecda</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Machine Learning Engineer II, Fulfillment, Matching and Positioning</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chester, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c1a1e7972c5914c</t>
+          <t>https://www.indeed.com/viewjob?jk=d50de39e70c8ab2c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Data Science Senior Associate - Digiops Analytics</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Copilot, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, A/B Testing</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b141def2a4008ee</t>
+          <t>https://www.indeed.com/viewjob?jk=98bfcbfe4a66b804</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Coralogix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87e7016b10fbd950</t>
+          <t>https://www.indeed.com/viewjob?jk=3376b01d585c7a8a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Data Scientist II - AI for Analytics</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, PyTorch, Git, Snowflake, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b60a55b6790d732</t>
+          <t>https://www.indeed.com/viewjob?jk=79d602cd8483a91f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Machine Learning Engineer II, Ads Response Prediction</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aa0c79a7795c005</t>
+          <t>https://www.indeed.com/viewjob?jk=b87b4b00adedaf15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ruby On Rails Developer</t>
+          <t>Senior Machine Learning Engineer, Operations Research</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Power Home Remodeling</t>
+          <t>Instacart</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Conshohocken, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, PostgreSQL, MySQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, XGBoost, Keras, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fe03ce7799fc2f</t>
+          <t>https://www.indeed.com/viewjob?jk=5f15a673d775e67f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Platform Integrations</t>
+          <t>Java-Python-Senior Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Insight Software</t>
+          <t>Objectways Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, GitHub Actions, Git, SQL, R, Optimization</t>
+          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,112 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e02b6ba7889f82</t>
+          <t>https://www.indeed.com/viewjob?jk=df547742c859d8ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Shopping Experience (Search)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=245a510836513b0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1e61cfbd795f413</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CCaaS-Five9-GCP-Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Objectways Technologies</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa963d1e326a898f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-15.xlsx
+++ b/daily_matches/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python-AI_ML-GenAI- Senior Engineer</t>
+          <t>Gen AI / Agentic AI Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Kafka</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, GCP Vertex AI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f451b2d6561869</t>
+          <t>https://www.indeed.com/viewjob?jk=e48bc5dc948cf83d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bioinformatics Data Scientist</t>
+          <t>Software Engineer, AI &amp; Clinical Applications</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spectrix Analytical Services, LLC</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, Data Lake, FastAPI, Docker, Git, Python, SQL</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, FastAPI, Docker, CI/CD, Git, PySpark, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7716b1a79b7d737</t>
+          <t>https://www.indeed.com/viewjob?jk=afc93472e6a09eb2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Intern Agentic AI Developer (Summer 2026)</t>
+          <t>AI / ML Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, NY, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Gemini, FAISS, Pinecone, Prompt Engineering, Docker, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe812e6352b4299a</t>
+          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Marketing Decision Scientist II</t>
+          <t>GCP Cloud Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24fa6b84d831ce2</t>
+          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Big Data Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HackerTrail</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Kubernetes, Kafka, Python, R, Scala</t>
+          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a78e150cfaec939</t>
+          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Advisor, Data Scientist - CMC Data Products</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nintex</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, S3, Glue, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=884a331450111479</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7d2fe1cc6d991c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II, AI Labs &amp; Foundations</t>
+          <t>Data Scientist - remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FAISS, Pinecone, Docker, Kubernetes, CI/CD, Kafka, R, Scala</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=373129946e19ecda</t>
+          <t>https://www.indeed.com/viewjob?jk=c99b014c7af759c2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer II, Fulfillment, Matching and Positioning</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>COLLEGE OF CHARLESTON</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Docker, Kubernetes, Kafka, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Gemini, Copilot, Data Lake, Snowflake, Hadoop, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d50de39e70c8ab2c</t>
+          <t>https://www.indeed.com/viewjob?jk=cc02cced931b012c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate - Digiops Analytics</t>
+          <t>Sr. DevOps Engineer, Cloud Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Contoro Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Snowflake, Hadoop, Tableau, Python, SQL, R, A/B Testing</t>
+          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98bfcbfe4a66b804</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd7611eed8918ef</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Coralogix</t>
+          <t>Techster IT Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Kafka, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,137 +811,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3376b01d585c7a8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Scientist II - AI for Analytics</t>
+          <t>Advisor - Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, PyTorch, Git, Snowflake, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Pinecone, Data Lake, Kinesis, Snowflake, Databricks, Kafka, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79d602cd8483a91f</t>
+          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer II, Ads Response Prediction</t>
+          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Python, SQL, R, Scala, Optimization</t>
+          <t>LangChain, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b87b4b00adedaf15</t>
+          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer, Operations Research</t>
+          <t>Data Architect, Data Foundry</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, XGBoost, Keras, Python, SQL, R, Optimization</t>
+          <t>RAG, Pinecone, Data Lake, Kinesis, Snowflake, Databricks, Kafka, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f15a673d775e67f</t>
+          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java-Python-Senior Engineer</t>
+          <t>Gen AI Developer Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CI/CD, Jenkins, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, S3, EC2, Apache Airflow, CI/CD, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df547742c859d8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=4dcf42670cb2fbac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - Shopping Experience (Search)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=245a510836513b0e</t>
+          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Instacart</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Snowflake, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, Databricks, MySQL, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,357 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1e61cfbd795f413</t>
+          <t>https://www.indeed.com/viewjob?jk=1b54b698c911a4da</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CCaaS-Five9-GCP-Senior Engineer</t>
+          <t>Sr Data Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Objectways Technologies</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Westwood, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Tableau, Seaborn, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f917f7e25b97ee3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Sr Data Analyst</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Westwood, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Redshift, Kafka, Tableau, SQL, R, Java, Scala, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63588da79609b170</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (React)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Vertiv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Westerville, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Bioinformatics Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b40d9a22f815ce1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Software Engineer - Intermediate</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Equifax</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3acdb591c69f2713</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineer - Remote</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>UnitedHealthcare</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, BigQuery, CI/CD, GitHub Actions, Terraform, Git, BigQuery, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fa963d1e326a898f</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Databricks, PySpark, Kafka, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Data Scientist (Audit Analytics &amp; Automation)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HDR</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e7b8cd9666e4149</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Associate Data Scientist</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ab5690e5480a2bf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Advisor - Antibody Developability Validation &amp; Benchmarking</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, PyTorch, MLflow, R, Scala, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d05feb708a3d4432</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Blink Health</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=54706095e6bbcc0c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-15.xlsx
+++ b/daily_matches/job_matches_2026-06-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Gen AI / Agentic AI Developer</t>
+          <t>Senior Engineer, Applied AI &amp; Engineering Platforms</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Mistral, FAISS, Pinecone, Prompt Engineering, GCP Vertex AI</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, Prompt Engineering</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e48bc5dc948cf83d</t>
+          <t>https://www.indeed.com/viewjob?jk=7772b1f0bcb3a34f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, AI &amp; Clinical Applications</t>
+          <t>Sr. Software Engineer, AI Enablement</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Prompt Engineering, FastAPI, Docker, CI/CD, Git, PySpark, PostgreSQL</t>
+          <t>Generative AI, LangChain, RAG, Gemini, Copilot, TensorFlow, PyTorch, EC2, Kubernetes, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afc93472e6a09eb2</t>
+          <t>https://www.indeed.com/viewjob?jk=39fc72f8c9966e63</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI / ML Platform Engineer</t>
+          <t>Delivery Engineer - Data</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Ollion</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RAG, Glue, Redshift, BigQuery, Synapse, CI/CD, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62f90292ebb892f9</t>
+          <t>https://www.indeed.com/viewjob?jk=445761cb9a4d745b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GCP Cloud Architect</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bridgewater, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git</t>
+          <t>Data Scientist, RAG, MLflow, Kubernetes, Apache Airflow, CI/CD, GitHub Actions, Git, Databricks, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e132f20ebda73040</t>
+          <t>https://www.indeed.com/viewjob?jk=c12ffd5ffac2fa61</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Big Data Developer</t>
+          <t>DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>CPI Security</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d11a857f86418907</t>
+          <t>https://www.indeed.com/viewjob?jk=45c0dd66780ebceb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Advisor, Data Scientist - CMC Data Products</t>
+          <t>Media DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Fox Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, S3, Glue, Data Lake, CI/CD, GitHub Actions, Git, Databricks, Python</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7d2fe1cc6d991c</t>
+          <t>https://www.indeed.com/viewjob?jk=07118df6f35d34c4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Scientist - remote</t>
+          <t>Senior Software Engineer - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, CI/CD, Git, Python</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c99b014c7af759c2</t>
+          <t>https://www.indeed.com/viewjob?jk=83d2add02c5d6a67</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>COLLEGE OF CHARLESTON</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, Data Lake, Snowflake, Hadoop, Tableau, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, Data Lake, Apache Airflow, Git, PySpark, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc02cced931b012c</t>
+          <t>https://www.indeed.com/viewjob?jk=4d72a782e1d37555</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer, Cloud Platform</t>
+          <t>Data Engineer - Databricks (No Sponsorship Available)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Contoro Inc.</t>
+          <t>Heritage Construction + Materials</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, CI/CD, Terraform, Kafka, Python, SQL, R</t>
+          <t>RAG, Docker, CI/CD, Snowflake, Databricks, PySpark, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd7611eed8918ef</t>
+          <t>https://www.indeed.com/viewjob?jk=ac337d846258b00f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Techster IT Services</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Git, Databricks, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, BigQuery, CI/CD, BigQuery, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,137 +811,137 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3e422f581c3da41</t>
+          <t>https://www.indeed.com/viewjob?jk=1e1f719034b114e8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Advisor - Data Architect, Data Foundry</t>
+          <t>Frontend Engineer - Eden Prairie, MN/Hartford, CT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Data Lake, Kinesis, Snowflake, Databricks, Kafka, MongoDB, SQL, R</t>
+          <t>RAG, Copilot, S3, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c0373d1531b5796</t>
+          <t>https://www.indeed.com/viewjob?jk=964fe5cf80f12d95</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Engineer - MLOps &amp; Scientific Platforms - Data Foundry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LangChain, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, Cortex, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8fe151d5009e163</t>
+          <t>https://www.indeed.com/viewjob?jk=ac67a8cdebaece5b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect, Data Foundry</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Pinecone, Data Lake, Kinesis, Snowflake, Databricks, Kafka, MongoDB, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41a54aeef7c675fb</t>
+          <t>https://www.indeed.com/viewjob?jk=15f01adfcabdb36b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gen AI Developer Specialist</t>
+          <t>Advanced Analyst II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Meijer</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Apache Airflow, CI/CD, Python, R, Java, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, NLTK, Azure ML, Synapse, Git, Databricks, PySpark, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dcf42670cb2fbac</t>
+          <t>https://www.indeed.com/viewjob?jk=05fbf2d88cec47e3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Nebius</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, CI/CD, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df14fd351162190b</t>
+          <t>https://www.indeed.com/viewjob?jk=31f00e6c0725b88e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data/AI Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Databricks, MySQL, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, CI/CD, GitHub Actions, Git, Snowflake, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b54b698c911a4da</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2ad5c9440bf6f4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Senior SDET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>WITS America, Corp.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westwood, MA, US USA</t>
+          <t>Lake Forest, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Tableau, Seaborn, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f917f7e25b97ee3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ae096059d84d3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr Data Analyst</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Westwood, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Redshift, Kafka, Tableau, SQL, R, Java, Scala, A/B Testing</t>
+          <t>RAG, Copilot, Apache Airflow, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63588da79609b170</t>
+          <t>https://www.indeed.com/viewjob?jk=e06ff1e4f7c4be37</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full Stack Developer (React)</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, R, Java, Scala</t>
+          <t>RAG, Copilot, Apache Airflow, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81c8bd0e76c2eafa</t>
+          <t>https://www.indeed.com/viewjob?jk=f0afe24b56752f5e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Bioinformatics Platform Engineer</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
+          <t>RAG, Copilot, Apache Airflow, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b40d9a22f815ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=2fac56f9c738b06f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Data and Analytics Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Velir</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Python, R, Java, Scala</t>
+          <t>RAG, Copilot, Apache Airflow, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3acdb591c69f2713</t>
+          <t>https://www.indeed.com/viewjob?jk=705c948fee159e46</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote</t>
+          <t>Data Engineer - Azure, Databricks</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Databricks, PySpark, Kafka, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, Synapse, CI/CD, Git, Databricks, PySpark, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,67 +1231,67 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f023a5570dfcdab7</t>
+          <t>https://www.indeed.com/viewjob?jk=4cd7bc7854e61f88</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Scientist (Audit Analytics &amp; Automation)</t>
+          <t>SDET Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Brookfield, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e7b8cd9666e4149</t>
+          <t>https://www.indeed.com/viewjob?jk=6636661aa7abd3c3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>AI Solutions Engineer, Global</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,77 +1301,637 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab5690e5480a2bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=84b6a61587d086b4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Advisor - Antibody Developability Validation &amp; Benchmarking</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>POOLCORP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Covington, LA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, PyTorch, MLflow, R, Scala, Optimization, Bayesian, Hypothesis Testing</t>
+          <t>RAG, CI/CD, Git, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d05feb708a3d4432</t>
+          <t>https://www.indeed.com/viewjob?jk=dd29f70b3f487233</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Network Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blink Health</t>
+          <t>Revelation Pharma</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Pensacola, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Prompt Engineering, S3, MLflow, R, Scala, Optimization, Bayesian, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d7a3bc1a36a32fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Sr. Machine Learning Operations Specialist</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BJ's Wholesale Club</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Marlborough, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Redshift, CI/CD, Databricks, Redshift, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748e65bce9525e22</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Big Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LiveRamp</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=315e465df1337d36</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Synapse, Dataflow, CI/CD, Git, Databricks, Power BI, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7aa2706b744b073</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LVT (LiveView Technologies)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce5abfceb8bf9861</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Scientist I/II, Bioinformatics</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Lila Sciences</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, S3, EC2, Kubernetes, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50a364e46ecf8776</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Golang)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HARBOR IT</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, AKS, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2c553186fe210405</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Tool / Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, Databricks, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f32d27ff410b6716</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, AWS SageMaker, NoSQL, Python, SQL, R, Scala, Bayesian</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f89fa56e047ba96</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>WPP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, MongoDB, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3786b5f0ad1a17e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AI Core Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>DTN</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
         <v>10</v>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54706095e6bbcc0c</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Prompt Engineering, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e944fc2c3393cb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Associate Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Park Place Technologies</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Highland Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Azure ML, Synapse, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d4bed2c4d60f7b8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Park Place Technologies</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Highland Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, Synapse, Data Lake, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=174d731f6e10489b</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Associate Data Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Park Place Technologies</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Highland Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, Azure ML, Synapse, Data Lake, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d9cc1afb56459f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Associate Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Park Place Technologies</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Highland Heights, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Azure ML, Synapse, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e7b1e172a54dd05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>APIM Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>American Electric Power</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9976e83c3b138cd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Search and Recommendations</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb05ba56bd11adde</t>
         </is>
       </c>
     </row>
